--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_344_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_344_R35.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.525700000000001</v>
+        <v>8.738200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4601</v>
+        <v>6.7037</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0656</v>
+        <v>2.0346</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6154</v>
+        <v>6.5272</v>
       </c>
       <c r="H2" t="n">
-        <v>1.587</v>
+        <v>3.7837</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0284</v>
+        <v>2.7435</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8223</v>
+        <v>5.8519</v>
       </c>
       <c r="K2" t="n">
-        <v>1.684</v>
+        <v>3.7342</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1383</v>
+        <v>2.1177</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7931</v>
+        <v>0.6753</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.097</v>
+        <v>0.0495</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8901</v>
+        <v>0.6258</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4643</v>
+        <v>0.3734</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2794</v>
+        <v>-0.1845</v>
       </c>
       <c r="U2" t="n">
-        <v>0.185</v>
+        <v>0.5579</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7501</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7501</v>
+        <v>2.428</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.2515</v>
+        <v>8.465299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0825</v>
+        <v>5.2989</v>
       </c>
       <c r="F3" t="n">
-        <v>2.169</v>
+        <v>3.1664</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5272</v>
+        <v>5.6154</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7837</v>
+        <v>1.587</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7435</v>
+        <v>4.0284</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8519</v>
+        <v>4.8223</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7342</v>
+        <v>1.684</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1177</v>
+        <v>3.1383</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6753</v>
+        <v>0.7931</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0495</v>
+        <v>-0.097</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6258</v>
+        <v>0.8901</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1133</v>
+        <v>0.4039</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8057</v>
+        <v>0.1182</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6923</v>
+        <v>0.2858</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.7501</v>
       </c>
       <c r="W3" t="n">
-        <v>2.428</v>
+        <v>1.7501</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6474</v>
+        <v>3.2776</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6511</v>
+        <v>1.0796</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9963</v>
+        <v>2.1979</v>
       </c>
       <c r="G4" t="n">
         <v>2.7449</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7934</v>
+        <v>-0.1632</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.731</v>
+        <v>-0.3025</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0624</v>
+        <v>0.1393</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1566</v>
+        <v>0.6483</v>
       </c>
       <c r="E5" t="n">
-        <v>1.478</v>
+        <v>0.8017</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3214</v>
+        <v>-0.1534</v>
       </c>
       <c r="G5" t="n">
         <v>2.1085</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2535</v>
+        <v>-0.7617</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0499</v>
+        <v>0.3736</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3034</v>
+        <v>-1.1354</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9304</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2086</v>
+        <v>0.5625</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4081</v>
+        <v>-1.0542</v>
       </c>
       <c r="F6" t="n">
         <v>1.6167</v>
@@ -922,10 +922,10 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1573</v>
+        <v>0.5111</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4323</v>
+        <v>-0.0784</v>
       </c>
       <c r="U6" t="n">
         <v>0.5895</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2039</v>
+        <v>-0.044</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0741</v>
+        <v>1.3896</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.278</v>
+        <v>-1.4336</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0986</v>
+        <v>1.2465</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3625</v>
+        <v>0.1357</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7361</v>
+        <v>1.1108</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3462</v>
+        <v>1.5899</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9745</v>
+        <v>0.1078</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3717</v>
+        <v>1.4821</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2476</v>
+        <v>-0.3434</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.612</v>
+        <v>0.0279</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.3713</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.854</v>
+        <v>-1.3781</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1845</v>
+        <v>-0.2003</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6695</v>
+        <v>-1.1778</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.7527</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>J. AYAYI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5233</v>
+        <v>-0.2709</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8431</v>
+        <v>-0.6091</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3664</v>
+        <v>0.3382</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2465</v>
+        <v>-0.667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1357</v>
+        <v>0.5041</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1108</v>
+        <v>-1.1711</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5899</v>
+        <v>-0.6956</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1078</v>
+        <v>0.0539</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4821</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3434</v>
+        <v>0.0287</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0279</v>
+        <v>0.4502</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3713</v>
+        <v>-0.4216</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8574</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7468</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1105</v>
+        <v>-0.6183</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. AYAYI</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6823</v>
+        <v>-0.4488</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9197</v>
+        <v>4.0308</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2374</v>
+        <v>-4.4797</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.667</v>
+        <v>3.0986</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5041</v>
+        <v>2.3625</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1711</v>
+        <v>0.7361</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6956</v>
+        <v>4.3462</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0539</v>
+        <v>2.9745</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7495000000000001</v>
+        <v>1.3717</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0287</v>
+        <v>-1.2476</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4502</v>
+        <v>-0.612</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4216</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9432</v>
+        <v>-1.0989</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.224</v>
+        <v>-0.2278</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7191</v>
+        <v>-0.8711</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. STEVENS</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.651</v>
+        <v>-2.1499</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.568</v>
+        <v>-0.701</v>
       </c>
       <c r="F10" t="n">
-        <v>1.917</v>
+        <v>-1.449</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6928</v>
+        <v>-0.9774</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2245</v>
+        <v>-1.911</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9172</v>
+        <v>0.9336</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2136</v>
+        <v>0.549</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9614</v>
+        <v>-0.7023</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.175</v>
+        <v>1.2514</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4791</v>
+        <v>-1.5265</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7369</v>
+        <v>-1.2087</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2578</v>
+        <v>-0.3178</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2041</v>
+        <v>-0.4766</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0553</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1488</v>
+        <v>-0.3864</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>L. STEVENS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8969</v>
+        <v>-2.1819</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3471</v>
+        <v>-3.7292</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5498</v>
+        <v>1.5473</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9774</v>
+        <v>-1.6928</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.911</v>
+        <v>0.2245</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9336</v>
+        <v>-1.9172</v>
       </c>
       <c r="J11" t="n">
-        <v>0.549</v>
+        <v>-1.2136</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7023</v>
+        <v>0.9614</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2514</v>
+        <v>-2.175</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5265</v>
+        <v>-0.4791</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2087</v>
+        <v>-0.7369</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3178</v>
+        <v>0.2578</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2236</v>
+        <v>0.6732</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2636</v>
+        <v>-0.1059</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4872</v>
+        <v>0.7791</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1798</v>
+        <v>-3.7524</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2837</v>
+        <v>-1.7555</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.896</v>
+        <v>-1.9968</v>
       </c>
       <c r="G12" t="n">
         <v>0.0321</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2315</v>
+        <v>-0.3411</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2636</v>
+        <v>-0.2082</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0321</v>
+        <v>-0.1329</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3558</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5614</v>
+        <v>-4.0059</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.849</v>
+        <v>-1.4952</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7124</v>
+        <v>-2.5108</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2887</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1104</v>
+        <v>-1.5549</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6721</v>
+        <v>-0.3183</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4383</v>
+        <v>-1.2366</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9304</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.091200000000001</v>
+        <v>8.838100000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>9.2133</v>
+        <v>9.960100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.121999999999999</v>
+        <v>-1.1222</v>
       </c>
       <c r="G14" t="n">
         <v>18.1724</v>
@@ -1525,7 +1525,7 @@
         <v>12.2487</v>
       </c>
       <c r="L14" t="n">
-        <v>8.196299999999999</v>
+        <v>8.196300000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-2.2724</v>
@@ -1537,7 +1537,7 @@
         <v>1.2725</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>1.159799999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.2368</v>
@@ -1546,10 +1546,10 @@
         <v>17.3965</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.0916</v>
+        <v>-4.3447</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.8846</v>
+        <v>-1.1379</v>
       </c>
       <c r="U14" t="n">
         <v>-3.2069</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8646</v>
+        <v>3.1144</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4446</v>
+        <v>4.1833</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5799</v>
+        <v>-1.0689</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8129</v>
+        <v>0.4952</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.509</v>
+        <v>0.6123</v>
       </c>
       <c r="I15" t="n">
-        <v>0.696</v>
+        <v>-0.1171</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2525</v>
+        <v>1.3424</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4468</v>
+        <v>1.6637</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6993</v>
+        <v>-0.3213</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0655</v>
+        <v>-0.8472</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0622</v>
+        <v>-1.0514</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0033</v>
+        <v>0.2042</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5358</v>
+        <v>1.0831</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0682</v>
+        <v>0.4799</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5324</v>
+        <v>0.6032</v>
       </c>
       <c r="V15" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3558</v>
+        <v>3.7527</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.569</v>
+        <v>2.8938</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5935</v>
+        <v>3.025</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0245</v>
+        <v>-0.1313</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4952</v>
+        <v>-1.2306</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6123</v>
+        <v>0.4861</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1171</v>
+        <v>-1.7166</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3424</v>
+        <v>1.0572</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6637</v>
+        <v>2.242</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3213</v>
+        <v>-1.1848</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8472</v>
+        <v>-2.2878</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0514</v>
+        <v>-1.756</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2042</v>
+        <v>-0.5319</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5377</v>
+        <v>0.4079</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1098</v>
+        <v>0.0553</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6475</v>
+        <v>0.3525</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>1.8608</v>
       </c>
       <c r="W16" t="n">
-        <v>3.7527</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6805</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6692</v>
+        <v>2.2292</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0814</v>
+        <v>2.383</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4122</v>
+        <v>-0.1538</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2306</v>
+        <v>-0.8129</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4861</v>
+        <v>-1.509</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7166</v>
+        <v>0.696</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0572</v>
+        <v>0.2525</v>
       </c>
       <c r="K17" t="n">
-        <v>2.242</v>
+        <v>-0.4468</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1848</v>
+        <v>0.6993</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2878</v>
+        <v>-1.0655</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.756</v>
+        <v>-1.0622</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5319</v>
+        <v>-0.0033</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8167</v>
+        <v>0.9003</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8883</v>
+        <v>1.0067</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0716</v>
+        <v>-0.1063</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8608</v>
+        <v>1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1444</v>
+        <v>1.3558</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7472</v>
+        <v>1.8247</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1612</v>
+        <v>1.816</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.414</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.951</v>
+        <v>0.7347</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0479</v>
+        <v>-1.7046</v>
       </c>
       <c r="I18" t="n">
-        <v>0.097</v>
+        <v>2.4393</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0183</v>
+        <v>2.2649</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3396</v>
+        <v>-0.1275</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3213</v>
+        <v>2.3923</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9692</v>
+        <v>-1.5302</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3875</v>
+        <v>-1.5771</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4183</v>
+        <v>0.047</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q18" t="n">
+        <v>-2.3195</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.1598</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.1775</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.7984</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.9278</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.9843</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1429</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.1586</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-1.214</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-1.214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6173</v>
+        <v>-0.1235</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9903</v>
+        <v>1.0996</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.373</v>
+        <v>-1.2231</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7347</v>
+        <v>-0.951</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7046</v>
+        <v>-1.0479</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4393</v>
+        <v>0.097</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2649</v>
+        <v>0.0183</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1275</v>
+        <v>0.3396</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3923</v>
+        <v>-0.3213</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5302</v>
+        <v>-0.9692</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5771</v>
+        <v>-1.3875</v>
       </c>
       <c r="O19" t="n">
-        <v>0.047</v>
+        <v>0.4183</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0299</v>
+        <v>1.1136</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0272</v>
+        <v>1.0813</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0026</v>
+        <v>0.0323</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8658</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0579</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8079</v>
+        <v>-0.8751</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4263</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1713</v>
+        <v>0.1041</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9334</v>
+        <v>-1.6687</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3633</v>
+        <v>-1.1781</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2967</v>
+        <v>-0.4906</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8655</v>
+        <v>-3.7263</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.34</v>
+        <v>-2.2474</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5256</v>
+        <v>-1.4789</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0101</v>
+        <v>-0.7567</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1205</v>
+        <v>-1.7002</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1104</v>
+        <v>0.9435</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8555</v>
+        <v>-2.9696</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2195</v>
+        <v>-0.5473</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.636</v>
+        <v>-2.4223</v>
       </c>
       <c r="P21" t="n">
         <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3917</v>
+        <v>-1.6237</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4192</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8758</v>
+        <v>0.13</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5434</v>
+        <v>0.443</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1829</v>
+        <v>0.7886</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1107</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0289</v>
+        <v>-2.2252</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7063</v>
+        <v>-1.0521</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3226</v>
+        <v>-1.173</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7263</v>
+        <v>-2.8655</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2474</v>
+        <v>-1.34</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4789</v>
+        <v>-1.5256</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7567</v>
+        <v>-0.0101</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7002</v>
+        <v>-0.1205</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9435</v>
+        <v>0.1104</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.9696</v>
+        <v>-2.8555</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5473</v>
+        <v>-1.2195</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.4223</v>
+        <v>-1.636</v>
       </c>
       <c r="P22" t="n">
         <v>0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2129</v>
+        <v>1.1275</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6018</v>
+        <v>0.4604</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6111</v>
+        <v>0.6671</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7886</v>
+        <v>-1.1829</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>-0.1107</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.582</v>
+        <v>-2.4813</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.692</v>
+        <v>-2.2896</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.89</v>
+        <v>-0.1917</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5273</v>
+        <v>-3.9482</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.3901</v>
+        <v>0.6158</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1372</v>
+        <v>-4.5639</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4655</v>
+        <v>-0.7139</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5391</v>
+        <v>2.0033</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0736</v>
+        <v>-2.7172</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0618</v>
+        <v>-3.2343</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.851</v>
+        <v>-1.3875</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2108</v>
+        <v>-1.8468</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-2.7834</v>
       </c>
       <c r="R23" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.127</v>
+        <v>0.3224</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0668</v>
+        <v>-0.4007</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0602</v>
+        <v>0.7231</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5822</v>
+        <v>-3.0766</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2333</v>
+        <v>-2.2202</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.349</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.9482</v>
+        <v>-2.5273</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6158</v>
+        <v>-2.3901</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.5639</v>
+        <v>-0.1372</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7139</v>
+        <v>-1.4655</v>
       </c>
       <c r="K24" t="n">
-        <v>2.0033</v>
+        <v>-1.5391</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.7172</v>
+        <v>0.0736</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2343</v>
+        <v>-1.0618</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3875</v>
+        <v>-0.851</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8468</v>
+        <v>-0.2108</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7834</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7784</v>
+        <v>0.3785</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3443</v>
+        <v>0.405</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5658</v>
+        <v>-0.0266</v>
       </c>
       <c r="V24" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5661</v>
+        <v>-6.0721</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8227</v>
+        <v>-4.5868</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7434</v>
+        <v>-1.4853</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9143</v>
@@ -2404,13 +2404,13 @@
         <v>2.0876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9432</v>
+        <v>-0.4492</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9709</v>
+        <v>-0.735</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0277</v>
+        <v>0.2858</v>
       </c>
       <c r="V25" t="n">
         <v>1.4665</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.091099999999999</v>
+        <v>-6.518299999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>1.122099999999999</v>
+        <v>1.122199999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.213200000000001</v>
+        <v>-7.640499999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-18.1725</v>
@@ -2482,13 +2482,13 @@
         <v>16.2368</v>
       </c>
       <c r="S26" t="n">
-        <v>5.091300000000001</v>
+        <v>6.664099999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2067</v>
+        <v>3.2066</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8846</v>
+        <v>3.4573</v>
       </c>
       <c r="V26" t="n">
         <v>6.1496</v>
